--- a/code_and_data/pipeline_benchmarking/data/Table_S1.xlsx
+++ b/code_and_data/pipeline_benchmarking/data/Table_S1.xlsx
@@ -161,7 +161,7 @@
     <t>FlhF</t>
   </si>
   <si>
-    <t>PilZ/YcgR</t>
+    <t>PilZ</t>
   </si>
   <si>
     <t>FliT</t>
@@ -203,7 +203,7 @@
     <t>FlgR/FlrC/FlrA/FlaK/FlbD</t>
   </si>
   <si>
-    <t>SwrB/FlgW</t>
+    <t>SwrB</t>
   </si>
   <si>
     <t>SwrD</t>
@@ -212,10 +212,10 @@
     <t>FliY</t>
   </si>
   <si>
-    <t>Flagellar_put</t>
-  </si>
-  <si>
-    <t>yvyF</t>
+    <t>Putative</t>
+  </si>
+  <si>
+    <t>YvyF</t>
   </si>
   <si>
     <t>YviE/DUF6470</t>
@@ -233,7 +233,7 @@
     <t>MotK</t>
   </si>
   <si>
-    <t xml:space="preserve">MotX </t>
+    <t>MotX</t>
   </si>
   <si>
     <t>MotY</t>
@@ -269,7 +269,7 @@
     <t>FliZ</t>
   </si>
   <si>
-    <t>tPilZ/FlgX</t>
+    <t>FlgX</t>
   </si>
   <si>
     <t>FlhC</t>
@@ -281,7 +281,7 @@
     <t>DUF327</t>
   </si>
   <si>
-    <t>FapA/DUF342</t>
+    <t>FapA</t>
   </si>
   <si>
     <t>DUF1217</t>
@@ -314,7 +314,7 @@
     <t>FljA</t>
   </si>
   <si>
-    <t>SLT/Transglycosylase</t>
+    <t>Transglycosylase</t>
   </si>
   <si>
     <t>GCF_000092845.1</t>

--- a/code_and_data/pipeline_benchmarking/data/Table_S1.xlsx
+++ b/code_and_data/pipeline_benchmarking/data/Table_S1.xlsx
@@ -36563,7 +36563,7 @@
     <t>GCA_003599815.1_RJP56148.1</t>
   </si>
   <si>
-    <t>The  genome set was compiled using representative genomes defined in GTDB release v95. Genomes are arranged according to the GTDB tree v214.</t>
+    <t>The genome set was compiled using representative genomes defined in GTDB release 95. Genomes are arranged according to the GTDB tree v214.</t>
   </si>
 </sst>
 </file>

--- a/code_and_data/pipeline_benchmarking/data/Table_S1.xlsx
+++ b/code_and_data/pipeline_benchmarking/data/Table_S1.xlsx
@@ -36563,7 +36563,7 @@
     <t>GCA_003599815.1_RJP56148.1</t>
   </si>
   <si>
-    <t>The genome set was compiled using representative genomes defined in GTDB release 95. Genomes are arranged according to the GTDB tree v214.</t>
+    <t>The genome set was compiled using representative genomes defined in GTDB release 95. Genomes are arranged according to the GTDB tree r214.</t>
   </si>
 </sst>
 </file>
